--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38B75A52-CC69-A743-8EC0-94C5412F20D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB586EF9-EDC7-2A44-8DCD-58BAEE63D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="680" windowWidth="28040" windowHeight="16920" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="11300" yWindow="660" windowWidth="18620" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,143 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="44">
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>width_between_legs</t>
+  </si>
+  <si>
+    <t>hock_height</t>
+  </si>
+  <si>
+    <t>leg_height</t>
+  </si>
+  <si>
+    <t>leg_curve.R</t>
+  </si>
+  <si>
+    <t>udder.curve.R</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>n_points</t>
+  </si>
+  <si>
+    <t>a_param</t>
+  </si>
+  <si>
+    <t>d_param</t>
+  </si>
+  <si>
+    <t>s_param</t>
+  </si>
+  <si>
+    <t>l_param</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>teat_length_score</t>
+  </si>
+  <si>
+    <t>teats_curve.R</t>
+  </si>
+  <si>
+    <t>pelvic.curve.R</t>
+  </si>
+  <si>
+    <t>medial_curve.R</t>
+  </si>
+  <si>
+    <t>ui.teats.R</t>
+  </si>
+  <si>
+    <t>app.R</t>
+  </si>
+  <si>
+    <t>top_y</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>med_o</t>
+  </si>
+  <si>
+    <t>med_p</t>
+  </si>
+  <si>
+    <t>med_q</t>
+  </si>
+  <si>
+    <t>arch_a</t>
+  </si>
+  <si>
+    <t>arch_d</t>
+  </si>
+  <si>
+    <t>arch_s</t>
+  </si>
+  <si>
+    <t>o_param</t>
+  </si>
+  <si>
+    <t>p_param</t>
+  </si>
+  <si>
+    <t>q_param</t>
+  </si>
+  <si>
+    <t>r_param</t>
+  </si>
+  <si>
+    <t>j_param</t>
+  </si>
+  <si>
+    <t>u_param</t>
+  </si>
+  <si>
+    <t>h_param</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +542,482 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C34CDA-7263-D04D-BE92-B36483DF3D5D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="4" max="4" width="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB586EF9-EDC7-2A44-8DCD-58BAEE63D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9EBD40-152D-BA4D-975D-4A2D84D7093B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11300" yWindow="660" windowWidth="18620" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29920" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
   <si>
     <t>Definition</t>
   </si>
@@ -62,36 +62,12 @@
     <t>leg_curve.R</t>
   </si>
   <si>
-    <t>udder.curve.R</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>l</t>
   </si>
   <si>
     <t>n_points</t>
   </si>
   <si>
-    <t>a_param</t>
-  </si>
-  <si>
-    <t>d_param</t>
-  </si>
-  <si>
-    <t>s_param</t>
-  </si>
-  <si>
-    <t>l_param</t>
-  </si>
-  <si>
     <t>j</t>
   </si>
   <si>
@@ -113,64 +89,118 @@
     <t>teats_curve.R</t>
   </si>
   <si>
-    <t>pelvic.curve.R</t>
-  </si>
-  <si>
     <t>medial_curve.R</t>
   </si>
   <si>
-    <t>ui.teats.R</t>
-  </si>
-  <si>
     <t>app.R</t>
   </si>
   <si>
     <t>top_y</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>med_o</t>
-  </si>
-  <si>
-    <t>med_p</t>
-  </si>
-  <si>
-    <t>med_q</t>
-  </si>
-  <si>
-    <t>arch_a</t>
-  </si>
-  <si>
-    <t>arch_d</t>
-  </si>
-  <si>
-    <t>arch_s</t>
-  </si>
-  <si>
-    <t>o_param</t>
-  </si>
-  <si>
-    <t>p_param</t>
-  </si>
-  <si>
-    <t>q_param</t>
-  </si>
-  <si>
-    <t>r_param</t>
-  </si>
-  <si>
-    <t>j_param</t>
-  </si>
-  <si>
-    <t>u_param</t>
-  </si>
-  <si>
-    <t>h_param</t>
+    <t>udder_curve.R</t>
+  </si>
+  <si>
+    <t>pelvic_curve.R</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>arch_roundness</t>
+  </si>
+  <si>
+    <t>arch_height</t>
+  </si>
+  <si>
+    <t>arch_shape</t>
+  </si>
+  <si>
+    <t>leg_width</t>
+  </si>
+  <si>
+    <t>teat_placement</t>
+  </si>
+  <si>
+    <t>teat_roundness</t>
+  </si>
+  <si>
+    <t>udder_floor_height</t>
+  </si>
+  <si>
+    <t>teat_length</t>
+  </si>
+  <si>
+    <t>teat_diameter</t>
+  </si>
+  <si>
+    <t>closeness_of_halves</t>
+  </si>
+  <si>
+    <t>depth_of_medial</t>
+  </si>
+  <si>
+    <t>bot_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. </t>
+  </si>
+  <si>
+    <t>Controls the distance between the ground and the hock, or the rear knee joint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the total length of the leg visualization. This number doesn't need to precise, as what matters is that the legs are long enough to span the entire visualization - the length of the legs is not connected to a specific score. </t>
+  </si>
+  <si>
+    <t>vertical height of the arch (d in desmos)</t>
+  </si>
+  <si>
+    <t>controls the curvature/steepness of the arch (a in desmos)</t>
+  </si>
+  <si>
+    <t>attachment shape; must be greater than leg_width</t>
+  </si>
+  <si>
+    <t>horizontal span of the arch</t>
+  </si>
+  <si>
+    <t>distance from center to each teat (halves the teat when 0)</t>
+  </si>
+  <si>
+    <t>distance between parabola roots; controls teat width</t>
+  </si>
+  <si>
+    <t>where the udder floor sits (shared with medial)</t>
+  </si>
+  <si>
+    <t>how far the teat hangs below the udder floor</t>
+  </si>
+  <si>
+    <t>width scaling of the teat</t>
+  </si>
+  <si>
+    <t>horizontal boundary for the plot x-range</t>
+  </si>
+  <si>
+    <t>horizontal distance between the legs, constrained to 0–20 inches</t>
+  </si>
+  <si>
+    <t>Closed polygon for the region above the pelvic arch, capped at top_y</t>
+  </si>
+  <si>
+    <t>height of the udder floor above the ground baseline</t>
+  </si>
+  <si>
+    <t>how close the two udder halves are to each other</t>
+  </si>
+  <si>
+    <t>depth/curvature of the medial suspensory ligament</t>
+  </si>
+  <si>
+    <t>horizontal distance between the legs</t>
+  </si>
+  <si>
+    <t>height of the rear knee joint above the ground baseline</t>
   </si>
 </sst>
 </file>
@@ -542,12 +572,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C34CDA-7263-D04D-BE92-B36483DF3D5D}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="96" customWidth="1"/>
+    <col min="3" max="3" width="71.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -561,12 +591,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -576,10 +609,13 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -587,434 +623,344 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
         <v>17</v>
-      </c>
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9EBD40-152D-BA4D-975D-4A2D84D7093B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A392915-E458-0140-9D38-985A5735DBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29920" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29920" windowHeight="16920" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B147B1AF-9ADD-8246-8A5E-F710B4881610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A00868-7A79-774F-95A8-361C11A10CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29920" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="8500" yWindow="660" windowWidth="21420" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
   <si>
     <t>Definition</t>
   </si>
@@ -152,30 +152,9 @@
     <t xml:space="preserve">Controls the total length of the leg visualization. This number doesn't need to precise, as what matters is that the legs are long enough to span the entire visualization - the length of the legs is not connected to a specific score. </t>
   </si>
   <si>
-    <t>vertical height of the arch (d in desmos)</t>
-  </si>
-  <si>
-    <t>controls the curvature/steepness of the arch (a in desmos)</t>
-  </si>
-  <si>
     <t>attachment shape; must be greater than leg_width</t>
   </si>
   <si>
-    <t>horizontal span of the arch</t>
-  </si>
-  <si>
-    <t>distance from center to each teat (halves the teat when 0)</t>
-  </si>
-  <si>
-    <t>distance between parabola roots; controls teat width</t>
-  </si>
-  <si>
-    <t>where the udder floor sits (shared with medial)</t>
-  </si>
-  <si>
-    <t>how far the teat hangs below the udder floor</t>
-  </si>
-  <si>
     <t>width scaling of the teat</t>
   </si>
   <si>
@@ -188,9 +167,6 @@
     <t>Closed polygon for the region above the pelvic arch, capped at top_y</t>
   </si>
   <si>
-    <t>height of the udder floor above the ground baseline</t>
-  </si>
-  <si>
     <t>how close the two udder halves are to each other</t>
   </si>
   <si>
@@ -201,6 +177,39 @@
   </si>
   <si>
     <t>height of the rear knee joint above the ground baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the curvature and steepness of the udder arch. Relates to "a" variable in Desmos. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the vertical height of the udder arch; correlates to the "d" variable in Desmos. </t>
+  </si>
+  <si>
+    <t>Controls the distance from the midline of the udder (think the highest point of the medial) to each teat. Correlates to the "j" variable in Desmos. When this variable is zero, the teats are so close together only half of a teat shows up right on the midline of the udder, creating the illusion of a singular teat right on the midline of the udder in a cyclops fashion.</t>
+  </si>
+  <si>
+    <t>leg_curve.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. In the udder_arch.R script, it affects the horizontal span of the udder arch. </t>
+  </si>
+  <si>
+    <t>medial_curve.R, pelvic_curve.R, teats_curve.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets the step size for the points that create the polygons and lines. A higher value under this valuable will create more continuous lines. </t>
+  </si>
+  <si>
+    <t>Sets the distance between parabola roots (where the arms of the parabola, or teat, crosses the x axis); controls teat width. Correlates to "h" variable in Desmos.</t>
+  </si>
+  <si>
+    <t>medial_curve.R, teats_curve.R</t>
+  </si>
+  <si>
+    <t>where the udder floor sits (shared with medial). height of the udder floor above the ground baseline</t>
+  </si>
+  <si>
+    <t>Determines the length of the teat; the distance between the tip of the teat and the udder floor.</t>
   </si>
 </sst>
 </file>
@@ -572,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C34CDA-7263-D04D-BE92-B36483DF3D5D}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="25.33203125" customWidth="1"/>
@@ -656,7 +665,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -667,7 +676,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -678,7 +687,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -686,10 +695,10 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -697,7 +706,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -708,7 +720,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -719,7 +731,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -727,10 +739,10 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -741,7 +753,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -752,7 +764,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -763,7 +775,7 @@
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -792,132 +804,129 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
-      <c r="C28" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
-      <c r="C29" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
@@ -925,41 +934,9 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
         <v>17</v>
       </c>
     </row>

--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A00868-7A79-774F-95A8-361C11A10CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746E5C7B-2E65-4B4F-AB4C-D5C8CEB65974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8500" yWindow="660" windowWidth="21420" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="500" yWindow="840" windowWidth="29260" windowHeight="16620" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>Definition</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Location</t>
   </si>
   <si>
-    <t>width_between_legs</t>
-  </si>
-  <si>
     <t>hock_height</t>
   </si>
   <si>
@@ -62,27 +59,9 @@
     <t>leg_curve.R</t>
   </si>
   <si>
-    <t>l</t>
-  </si>
-  <si>
     <t>n_points</t>
   </si>
   <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
     <t>teat_length_score</t>
   </si>
   <si>
@@ -92,9 +71,6 @@
     <t>medial_curve.R</t>
   </si>
   <si>
-    <t>app.R</t>
-  </si>
-  <si>
     <t>top_y</t>
   </si>
   <si>
@@ -143,9 +119,6 @@
     <t>bot_y</t>
   </si>
   <si>
-    <t xml:space="preserve">Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. </t>
-  </si>
-  <si>
     <t>Controls the distance between the ground and the hock, or the rear knee joint.</t>
   </si>
   <si>
@@ -158,12 +131,6 @@
     <t>width scaling of the teat</t>
   </si>
   <si>
-    <t>horizontal boundary for the plot x-range</t>
-  </si>
-  <si>
-    <t>horizontal distance between the legs, constrained to 0–20 inches</t>
-  </si>
-  <si>
     <t>Closed polygon for the region above the pelvic arch, capped at top_y</t>
   </si>
   <si>
@@ -173,12 +140,6 @@
     <t>depth/curvature of the medial suspensory ligament</t>
   </si>
   <si>
-    <t>horizontal distance between the legs</t>
-  </si>
-  <si>
-    <t>height of the rear knee joint above the ground baseline</t>
-  </si>
-  <si>
     <t xml:space="preserve">Controls the curvature and steepness of the udder arch. Relates to "a" variable in Desmos. </t>
   </si>
   <si>
@@ -188,12 +149,6 @@
     <t>Controls the distance from the midline of the udder (think the highest point of the medial) to each teat. Correlates to the "j" variable in Desmos. When this variable is zero, the teats are so close together only half of a teat shows up right on the midline of the udder, creating the illusion of a singular teat right on the midline of the udder in a cyclops fashion.</t>
   </si>
   <si>
-    <t>leg_curve.R, udder_curve.R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. In the udder_arch.R script, it affects the horizontal span of the udder arch. </t>
-  </si>
-  <si>
     <t>medial_curve.R, pelvic_curve.R, teats_curve.R, udder_curve.R</t>
   </si>
   <si>
@@ -203,25 +158,53 @@
     <t>Sets the distance between parabola roots (where the arms of the parabola, or teat, crosses the x axis); controls teat width. Correlates to "h" variable in Desmos.</t>
   </si>
   <si>
-    <t>medial_curve.R, teats_curve.R</t>
-  </si>
-  <si>
     <t>where the udder floor sits (shared with medial). height of the udder floor above the ground baseline</t>
   </si>
   <si>
     <t>Determines the length of the teat; the distance between the tip of the teat and the udder floor.</t>
+  </si>
+  <si>
+    <t>app. R, teats_curve.R</t>
+  </si>
+  <si>
+    <t>app. R, medial_curve.R, teats_curve.R</t>
+  </si>
+  <si>
+    <t>app. R, udder_curve.R</t>
+  </si>
+  <si>
+    <t>app.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t>app.R, leg_curve.R, medial_curve.R</t>
+  </si>
+  <si>
+    <t>app. R,medial_curve.R, teats_curve.R</t>
+  </si>
+  <si>
+    <t>app.R, leg_curve.R, medial_curve.R, pelvic_curve.R, teats_curve.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t>Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. In the udder_arch.R script, it affects the horizontal span of the udder arch. Values limited to 0 to 20 inches. Teats: horizontal boundary for the plot x-range</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -245,8 +228,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C34CDA-7263-D04D-BE92-B36483DF3D5D}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="25.33203125" customWidth="1"/>
@@ -589,23 +573,23 @@
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
@@ -613,59 +597,56 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -673,10 +654,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -684,40 +665,40 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
@@ -725,222 +706,109 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
         <v>11</v>
       </c>
-      <c r="B33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C23">
+    <sortCondition ref="A2:A23"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746E5C7B-2E65-4B4F-AB4C-D5C8CEB65974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BBF273-DF53-0541-B771-92088DB620F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="840" windowWidth="29260" windowHeight="16620" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="15160" yWindow="660" windowWidth="14760" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>Definition</t>
   </si>
@@ -68,21 +68,12 @@
     <t>teats_curve.R</t>
   </si>
   <si>
-    <t>medial_curve.R</t>
-  </si>
-  <si>
     <t>top_y</t>
   </si>
   <si>
-    <t>udder_curve.R</t>
-  </si>
-  <si>
     <t>pelvic_curve.R</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>arch_roundness</t>
   </si>
   <si>
@@ -170,12 +161,6 @@
     <t>app. R, medial_curve.R, teats_curve.R</t>
   </si>
   <si>
-    <t>app. R, udder_curve.R</t>
-  </si>
-  <si>
-    <t>app.R, udder_curve.R</t>
-  </si>
-  <si>
     <t>app.R, leg_curve.R, medial_curve.R</t>
   </si>
   <si>
@@ -186,13 +171,19 @@
   </si>
   <si>
     <t>Controls the amount of space between the legs. Defined as the space between the inner boundary line of the two legs. In the udder_arch.R script, it affects the horizontal span of the udder arch. Values limited to 0 to 20 inches. Teats: horizontal boundary for the plot x-range</t>
+  </si>
+  <si>
+    <t>app.R, medial_curve.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t>app. R, medial_curve.R, udder_curve.R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -205,6 +196,13 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -228,9 +226,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C34CDA-7263-D04D-BE92-B36483DF3D5D}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="25.33203125" customWidth="1"/>
@@ -586,228 +585,199 @@
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
+      <c r="A17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>35</v>
+      <c r="A18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
+      <c r="C19" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C23">
-    <sortCondition ref="A2:A23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
+    <sortCondition ref="A2:A20"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/goat_data_dictionary.xlsx
+++ b/docs/goat_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camilachicatto/2026_startup_goats/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BBF273-DF53-0541-B771-92088DB620F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACFC480-958D-004F-B3D0-1F44C4B2CBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15160" yWindow="660" windowWidth="14760" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29920" windowHeight="18680" xr2:uid="{0DF32BC2-826F-6B48-94CE-D6017A50CA52}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Definition</t>
   </si>
@@ -116,21 +116,6 @@
     <t xml:space="preserve">Controls the total length of the leg visualization. This number doesn't need to precise, as what matters is that the legs are long enough to span the entire visualization - the length of the legs is not connected to a specific score. </t>
   </si>
   <si>
-    <t>attachment shape; must be greater than leg_width</t>
-  </si>
-  <si>
-    <t>width scaling of the teat</t>
-  </si>
-  <si>
-    <t>Closed polygon for the region above the pelvic arch, capped at top_y</t>
-  </si>
-  <si>
-    <t>how close the two udder halves are to each other</t>
-  </si>
-  <si>
-    <t>depth/curvature of the medial suspensory ligament</t>
-  </si>
-  <si>
     <t xml:space="preserve">Controls the curvature and steepness of the udder arch. Relates to "a" variable in Desmos. </t>
   </si>
   <si>
@@ -149,9 +134,6 @@
     <t>Sets the distance between parabola roots (where the arms of the parabola, or teat, crosses the x axis); controls teat width. Correlates to "h" variable in Desmos.</t>
   </si>
   <si>
-    <t>where the udder floor sits (shared with medial). height of the udder floor above the ground baseline</t>
-  </si>
-  <si>
     <t>Determines the length of the teat; the distance between the tip of the teat and the udder floor.</t>
   </si>
   <si>
@@ -164,9 +146,6 @@
     <t>app.R, leg_curve.R, medial_curve.R</t>
   </si>
   <si>
-    <t>app. R,medial_curve.R, teats_curve.R</t>
-  </si>
-  <si>
     <t>app.R, leg_curve.R, medial_curve.R, pelvic_curve.R, teats_curve.R, udder_curve.R</t>
   </si>
   <si>
@@ -177,13 +156,40 @@
   </si>
   <si>
     <t>app. R, medial_curve.R, udder_curve.R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets a high end vertical limit to the legs so they don't stretch out forever. By default is set to 3. </t>
+  </si>
+  <si>
+    <t>Sets a low end vertical limit to the elgs so that they don't stretch out forever. By default is set to -20.</t>
+  </si>
+  <si>
+    <t>Defines the upper boundary of the pelvic polygon; shape is capped at top_y.</t>
+  </si>
+  <si>
+    <t>Controls the width of the teat. Larger values make the teat (parabola) thinner, and smaller values make the teat wider.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter which converts linear appraisal scores into an actual teat length. </t>
+  </si>
+  <si>
+    <t>How wide the udder arch is. Determines how wide the arch is, wideness and openess. Must be greater than leg_width.</t>
+  </si>
+  <si>
+    <t>Depth and curvature of the medial suspensory ligament. How "high" up the medial suspensory ligament is towards the tail.</t>
+  </si>
+  <si>
+    <t>Moves the udder floor upwards or downwards towards the tail or ground, respectively.</t>
+  </si>
+  <si>
+    <t>Controls how close the two udder halves are to the midline.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,13 +202,6 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -229,7 +228,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,10 +587,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -599,10 +598,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -610,10 +609,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -623,17 +622,19 @@
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -641,10 +642,10 @@
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -652,7 +653,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -674,10 +675,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -685,10 +686,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -696,10 +697,10 @@
         <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -707,10 +708,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -720,17 +721,19 @@
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="2" t="s">
         <v>32</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -738,10 +741,10 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -751,7 +754,9 @@
       <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
@@ -761,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -769,10 +774,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
